--- a/new original/_Lang_Chinese/Lang/CN/Game/Game.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Game.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">weather_Rain</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">It begins to rain.</t>
@@ -12472,7 +12472,7 @@
     <t xml:space="preserve">反击！</t>
   </si>
   <si>
-    <t xml:space="preserve">命运拒绝#1的死亡。</t>
+    <t xml:space="preserve">命运拒绝了#1的死亡。</t>
   </si>
   <si>
     <t xml:space="preserve">#1名小妹妹启程去寻找新天地。</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Game.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Game.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">weather_Rain</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">It begins to rain.</t>
@@ -12472,7 +12472,7 @@
     <t xml:space="preserve">反击！</t>
   </si>
   <si>
-    <t xml:space="preserve">命运拒绝了#1的死亡。</t>
+    <t xml:space="preserve">命运拒绝#1的死亡。</t>
   </si>
   <si>
     <t xml:space="preserve">#1名小妹妹启程去寻找新天地。</t>
